--- a/Day_03/Answers/Day03_Core1_Assessment_MarkJhonAngeloLlanesCruz.xlsx
+++ b/Day_03/Answers/Day03_Core1_Assessment_MarkJhonAngeloLlanesCruz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a96f5c588f37a5dc/Desktop/MJ/TESDA/Day_03/Answers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_3942388BE9AC3879DF3525BB5B777CBD8A66A01B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0547AD80-9533-4B91-8E49-862D06EE7079}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_3942388BE9AC3879DF3525BB5B777CBD8A66A01B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31A5C871-78C6-4E3E-9F9E-7A2E5A4551F6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -598,7 +598,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -636,39 +636,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -709,6 +691,34 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2080,6 +2090,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2266,136 +2280,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
+      <c r="A4" s="1"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
+      <c r="A6" s="1"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
+      <c r="A9" s="1"/>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
+      <c r="A11" s="1"/>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
+      <c r="A15" s="1"/>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
+      <c r="A20" s="1"/>
     </row>
     <row r="21" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
+      <c r="A24" s="1"/>
     </row>
     <row r="25" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12"/>
+      <c r="A27" s="1"/>
     </row>
     <row r="28" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2423,832 +2437,832 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="4">
         <v>12</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="5">
         <v>7200</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="6">
         <v>20</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="7">
         <v>4800</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="4">
         <v>15</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="5">
         <v>2250</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="6">
         <v>8</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="7">
         <v>4800</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="4">
         <v>25</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="5">
         <v>1250</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="6">
         <v>18</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="7">
         <v>3600</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="4">
         <v>22</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="5">
         <v>2640</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="6">
         <v>10</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="7">
         <v>3500</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="4">
         <v>30</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="5">
         <v>1800</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="6">
         <v>14</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="7">
         <v>8400</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="4">
         <v>12</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="5">
         <v>2880</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="6">
         <v>35</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="7">
         <v>1750</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="4">
         <v>6</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="5">
         <v>2100</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="6">
         <v>25</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="7">
         <v>6000</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="4">
         <v>20</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="5">
         <v>2000</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="6">
         <v>18</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="7">
         <v>2700</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="4">
         <v>40</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="5">
         <v>3200</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="6">
         <v>22</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="7">
         <v>4400</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="4">
         <v>15</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="5">
         <v>9000</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="6">
         <v>28</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="7">
         <v>1680</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="4">
         <v>20</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="5">
         <v>2400</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="6">
         <v>10</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="7">
         <v>6000</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="4">
         <v>15</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="5">
         <v>3600</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="6">
         <v>28</v>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="7">
         <v>1400</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="4">
         <v>12</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="5">
         <v>4200</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="6">
         <v>32</v>
       </c>
-      <c r="F29" s="18">
+      <c r="F29" s="7">
         <v>1600</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="15">
+      <c r="E30" s="4">
         <v>22</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="5">
         <v>5280</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="6">
         <v>16</v>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="7">
         <v>9600</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="4">
         <v>20</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="5">
         <v>3000</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="6">
         <v>24</v>
       </c>
-      <c r="F33" s="18">
+      <c r="F33" s="7">
         <v>4800</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E34" s="15">
+      <c r="E34" s="4">
         <v>45</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="5">
         <v>3600</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="17">
+      <c r="E35" s="6">
         <v>35</v>
       </c>
-      <c r="F35" s="18">
+      <c r="F35" s="7">
         <v>2100</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="4">
         <v>25</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="5">
         <v>3000</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E37" s="17">
+      <c r="E37" s="6">
         <v>30</v>
       </c>
-      <c r="F37" s="18">
+      <c r="F37" s="7">
         <v>7200</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E38" s="15">
+      <c r="E38" s="4">
         <v>20</v>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="5">
         <v>12000</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E39" s="17">
+      <c r="E39" s="6">
         <v>3</v>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="7">
         <v>22500</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="4">
         <v>35</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="5">
         <v>8400</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E41" s="17">
+      <c r="E41" s="6">
         <v>30</v>
       </c>
-      <c r="F41" s="18">
+      <c r="F41" s="7">
         <v>4500</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="4">
         <v>10</v>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="5">
         <v>3500</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="17">
+      <c r="E43" s="6">
         <v>20</v>
       </c>
-      <c r="F43" s="18">
+      <c r="F43" s="7">
         <v>4800</v>
       </c>
     </row>
@@ -3272,119 +3286,119 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="8" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="9" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="8"/>
+      <c r="B4" s="19"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="11">
         <f>AVERAGE('Sales Data'!F4:F43)</f>
         <v>4735.75</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="11">
         <f>MEDIAN('Sales Data'!F4:F43)</f>
         <v>3600</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="11">
         <f>_xlfn.MODE.SNGL('Sales Data'!F4:F43)</f>
         <v>4800</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="8"/>
+      <c r="B9" s="19"/>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="12">
         <f>AVERAGE('Sales Data'!E4:E43)</f>
         <v>21.175000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="12">
         <f>MEDIAN('Sales Data'!E4:E43)</f>
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="13">
         <f>_xlfn.MODE.SNGL('Sales Data'!E4:E43)</f>
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="14" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
     </row>
     <row r="18" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3399,7 +3413,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:AX62"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -3407,487 +3421,488 @@
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="14" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="15" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="9" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5" t="s">
+      <c r="D5" s="29"/>
+      <c r="E5" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="29"/>
+      <c r="G5" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="29"/>
     </row>
     <row r="6" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6" s="24">
         <f>SUM('Sales Data'!F4:F43)</f>
         <v>189430</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="3">
+      <c r="B6" s="24"/>
+      <c r="C6" s="25">
         <f>AVERAGE('Sales Data'!F4:F43)</f>
         <v>4735.75</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="2" t="str">
+      <c r="D6" s="25"/>
+      <c r="E6" s="26" t="str">
         <f>INDEX(A9:A12,MATCH(MAX(B9:B12),B9:B12,0))</f>
         <v>Groceries</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="1">
+      <c r="F6" s="26"/>
+      <c r="G6" s="27">
         <f>COUNTA('Sales Data'!A4:A43)</f>
         <v>40</v>
       </c>
-      <c r="H6" s="1"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="G8" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="16" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="17">
         <f>SUMIF('Sales Data'!$C$4:$C$43,A9,'Sales Data'!$F$4:$F$43)</f>
         <v>96100</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="17">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D9,'Sales Data'!$F$4:$F$43)</f>
         <v>14250</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="13">
         <f>COUNTIFS('Sales Data'!$F$4:$F$43,"&gt;="&amp;0,'Sales Data'!$F$4:$F$43,"&lt;="&amp;2499)</f>
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="17">
         <f>SUMIF('Sales Data'!$C$4:$C$43,A10,'Sales Data'!$F$4:$F$43)</f>
         <v>55760</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="17">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D10,'Sales Data'!$F$4:$F$43)</f>
         <v>9650</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="13">
         <f>COUNTIFS('Sales Data'!$F$4:$F$43,"&gt;="&amp;2500,'Sales Data'!$F$4:$F$43,"&lt;="&amp;4999)</f>
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="17">
         <f>SUMIF('Sales Data'!$C$4:$C$43,A11,'Sales Data'!$F$4:$F$43)</f>
         <v>23640</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="17">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D11,'Sales Data'!$F$4:$F$43)</f>
         <v>7940</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="13">
         <f>COUNTIFS('Sales Data'!$F$4:$F$43,"&gt;="&amp;5000,'Sales Data'!$F$4:$F$43,"&lt;="&amp;7499)</f>
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="17">
         <f>SUMIF('Sales Data'!$C$4:$C$43,A12,'Sales Data'!$F$4:$F$43)</f>
         <v>13930</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="17">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D12,'Sales Data'!$F$4:$F$43)</f>
         <v>13030</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="13">
         <f>COUNTIFS('Sales Data'!$F$4:$F$43,"&gt;="&amp;7500,'Sales Data'!$F$4:$F$43,"&lt;="&amp;9999)</f>
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="17">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D13,'Sales Data'!$F$4:$F$43)</f>
         <v>10100</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="G13" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="13">
         <f>COUNTIFS('Sales Data'!$F$4:$F$43,"&gt;="&amp;10000,'Sales Data'!$F$4:$F$43,"&lt;="&amp;12499)</f>
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="17">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D14,'Sales Data'!$F$4:$F$43)</f>
         <v>10300</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="G14" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="13">
         <f>COUNTIFS('Sales Data'!$F$4:$F$43,"&gt;="&amp;12500,'Sales Data'!$F$4:$F$43,"&lt;="&amp;1000000)</f>
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="17">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D15,'Sales Data'!$F$4:$F$43)</f>
         <v>13080</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="17">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D16,'Sales Data'!$F$4:$F$43)</f>
         <v>11000</v>
       </c>
     </row>
     <row r="17" spans="4:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="17">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D17,'Sales Data'!$F$4:$F$43)</f>
         <v>11080</v>
       </c>
     </row>
     <row r="18" spans="4:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="17">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D18,'Sales Data'!$F$4:$F$43)</f>
         <v>17400</v>
       </c>
     </row>
     <row r="19" spans="4:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="17">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D19,'Sales Data'!$F$4:$F$43)</f>
         <v>15900</v>
       </c>
     </row>
     <row r="20" spans="4:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="17">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D20,'Sales Data'!$F$4:$F$43)</f>
         <v>55700</v>
       </c>
     </row>
     <row r="40" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H40" s="29" t="s">
+      <c r="H40" s="18" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="41" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H41" s="7" t="s">
+      <c r="H41" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
-      <c r="N41" s="7"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
     </row>
     <row r="42" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="7"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
     </row>
     <row r="43" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="7"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="20"/>
     </row>
     <row r="44" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
-      <c r="N44" s="7"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="20"/>
     </row>
     <row r="45" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="7"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="20"/>
+      <c r="N45" s="20"/>
     </row>
     <row r="46" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20"/>
+      <c r="M46" s="20"/>
+      <c r="N46" s="20"/>
     </row>
     <row r="47" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="7"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
+      <c r="M47" s="20"/>
+      <c r="N47" s="20"/>
     </row>
     <row r="48" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
-      <c r="N48" s="7"/>
-    </row>
-    <row r="49" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="7"/>
-    </row>
-    <row r="50" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
-      <c r="N50" s="7"/>
-    </row>
-    <row r="51" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
-      <c r="N51" s="7"/>
-    </row>
-    <row r="52" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
-    </row>
-    <row r="53" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
-      <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="7"/>
-    </row>
-    <row r="54" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
-      <c r="N54" s="7"/>
-    </row>
-    <row r="55" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="7"/>
-    </row>
-    <row r="56" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="29" t="s">
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
+      <c r="M48" s="20"/>
+      <c r="N48" s="20"/>
+    </row>
+    <row r="49" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+      <c r="K49" s="20"/>
+      <c r="L49" s="20"/>
+      <c r="M49" s="20"/>
+      <c r="N49" s="20"/>
+    </row>
+    <row r="50" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="20"/>
+      <c r="L50" s="20"/>
+      <c r="M50" s="20"/>
+      <c r="N50" s="20"/>
+    </row>
+    <row r="51" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+      <c r="M51" s="20"/>
+      <c r="N51" s="20"/>
+    </row>
+    <row r="52" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="20"/>
+      <c r="N52" s="20"/>
+    </row>
+    <row r="53" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20"/>
+      <c r="K53" s="20"/>
+      <c r="L53" s="20"/>
+      <c r="M53" s="20"/>
+      <c r="N53" s="20"/>
+    </row>
+    <row r="54" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="20"/>
+      <c r="L54" s="20"/>
+      <c r="M54" s="20"/>
+      <c r="N54" s="20"/>
+    </row>
+    <row r="55" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="20"/>
+      <c r="K55" s="20"/>
+      <c r="L55" s="20"/>
+      <c r="M55" s="20"/>
+      <c r="N55" s="20"/>
+    </row>
+    <row r="56" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="18" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
+    <row r="57" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-    </row>
-    <row r="58" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="7"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-    </row>
-    <row r="59" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="7"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-    </row>
-    <row r="60" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="7"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-    </row>
-    <row r="61" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="7"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-    </row>
-    <row r="62" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="7"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+    </row>
+    <row r="58" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="20"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+    </row>
+    <row r="59" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="20"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+    </row>
+    <row r="60" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="20"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+    </row>
+    <row r="61" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="20"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="20"/>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20"/>
+    </row>
+    <row r="62" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="20"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="AX62" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
     <mergeCell ref="A57:G62"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="H41:N55"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
   </mergeCells>
   <conditionalFormatting sqref="B9:B12">
     <cfRule type="dataBar" priority="2">

--- a/Day_03/Answers/Day03_Core1_Assessment_MarkJhonAngeloLlanesCruz.xlsx
+++ b/Day_03/Answers/Day03_Core1_Assessment_MarkJhonAngeloLlanesCruz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a96f5c588f37a5dc/Desktop/MJ/TESDA/Day_03/Answers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_3942388BE9AC3879DF3525BB5B777CBD8A66A01B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31A5C871-78C6-4E3E-9F9E-7A2E5A4551F6}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_3942388BE9AC3879DF3525BB5B777CBD8A66A01B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F136C9C-B8DF-48F6-A87C-B8009FF0A449}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -441,7 +441,7 @@
     <numFmt numFmtId="164" formatCode="\₱#,##0.00"/>
     <numFmt numFmtId="165" formatCode="\₱#,##0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -533,31 +533,45 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
-      <color rgb="FF1F3864"/>
+      <color theme="0"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FF1F3864"/>
+      <sz val="10"/>
+      <color theme="0"/>
       <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF1F3864"/>
-      <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -587,18 +601,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2E5496"/>
-        <bgColor rgb="FF2E75B6"/>
+        <fgColor rgb="FFA5A5A5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD6E4F0"/>
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -645,11 +658,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -683,44 +712,53 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Check Cell" xfId="1" builtinId="23"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -809,28 +847,35 @@
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1800" b="1" u="none" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
+              <a:rPr lang="en-US"/>
               <a:t>Total Sales by Product Category</a:t>
             </a:r>
           </a:p>
@@ -839,10 +884,30 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -866,15 +931,21 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln w="12600">
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="F9F9F9"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:round/>
+              <a:miter lim="800000"/>
             </a:ln>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
@@ -886,16 +957,21 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
                     </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -915,11 +991,15 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="0">
+                    <a:ln w="9525">
                       <a:solidFill>
-                        <a:srgbClr val="F9F9F9"/>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
                       </a:solidFill>
+                      <a:round/>
                     </a:ln>
+                    <a:effectLst/>
                   </c:spPr>
                 </c15:leaderLines>
               </c:ext>
@@ -980,7 +1060,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
+        <c:gapWidth val="315"/>
+        <c:overlap val="-40"/>
         <c:axId val="70228437"/>
         <c:axId val="72077576"/>
       </c:barChart>
@@ -991,26 +1072,51 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="1" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
+                  <a:rPr lang="en-US"/>
                   <a:t>Category</a:t>
                 </a:r>
               </a:p>
@@ -1019,34 +1125,56 @@
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
-            <a:ln w="0">
+            <a:ln>
               <a:noFill/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
                 </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1068,34 +1196,49 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
               <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="-5400000"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="1" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
+                  <a:rPr lang="en-US"/>
                   <a:t>Sales (₱)</a:t>
                 </a:r>
               </a:p>
@@ -1104,34 +1247,56 @@
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
-            <a:ln w="0">
+            <a:ln>
               <a:noFill/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="\₱#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
                 </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1142,12 +1307,11 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="0">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1156,15 +1320,32 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
       <a:round/>
     </a:ln>
+    <a:effectLst/>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -1178,28 +1359,35 @@
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1800" b="1" u="none" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
+              <a:rPr lang="en-US"/>
               <a:t>Monthly Sales Trend</a:t>
             </a:r>
           </a:p>
@@ -1208,10 +1396,30 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -1234,12 +1442,19 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="12600">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="BE4B48"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
@@ -1253,16 +1468,21 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
                     </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -1282,11 +1502,15 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="12600">
+                    <a:ln w="9525">
                       <a:solidFill>
-                        <a:srgbClr val="000000"/>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
                       </a:solidFill>
+                      <a:round/>
                     </a:ln>
+                    <a:effectLst/>
                   </c:spPr>
                 </c15:leaderLines>
               </c:ext>
@@ -1398,9 +1622,15 @@
         </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
-            <a:ln w="0">
-              <a:noFill/>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:hiLowLines>
         <c:smooth val="0"/>
@@ -1414,26 +1644,51 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="1" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
+                  <a:rPr lang="en-US"/>
                   <a:t>Month</a:t>
                 </a:r>
               </a:p>
@@ -1442,34 +1697,56 @@
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
-            <a:ln w="0">
+            <a:ln>
               <a:noFill/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
                 </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1491,34 +1768,49 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
               <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="-5400000"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="1" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
+                  <a:rPr lang="en-US"/>
                   <a:t>Sales (₱)</a:t>
                 </a:r>
               </a:p>
@@ -1527,34 +1819,56 @@
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
-            <a:ln w="0">
+            <a:ln>
               <a:noFill/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="\₱#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
                 </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1565,12 +1879,11 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="0">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1579,15 +1892,32 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
       <a:round/>
     </a:ln>
+    <a:effectLst/>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -1601,28 +1931,35 @@
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1800" b="1" u="none" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
+              <a:rPr lang="en-US"/>
               <a:t>Distribution of Sales Amounts (Histogram)</a:t>
             </a:r>
           </a:p>
@@ -1631,10 +1968,30 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -1658,15 +2015,21 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4BACC6"/>
-            </a:solidFill>
-            <a:ln w="12600">
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="F9F9F9"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:round/>
+              <a:miter lim="800000"/>
             </a:ln>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
@@ -1678,16 +2041,21 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
                     </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -1707,11 +2075,15 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="0">
+                    <a:ln w="9525">
                       <a:solidFill>
-                        <a:srgbClr val="F9F9F9"/>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
                       </a:solidFill>
+                      <a:round/>
                     </a:ln>
+                    <a:effectLst/>
                   </c:spPr>
                 </c15:leaderLines>
               </c:ext>
@@ -1784,7 +2156,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="0"/>
+        <c:gapWidth val="315"/>
+        <c:overlap val="-40"/>
         <c:axId val="98535875"/>
         <c:axId val="69757031"/>
       </c:barChart>
@@ -1795,26 +2168,51 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="1" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
+                  <a:rPr lang="en-US"/>
                   <a:t>Sales Amount Range</a:t>
                 </a:r>
               </a:p>
@@ -1823,34 +2221,56 @@
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
-            <a:ln w="0">
+            <a:ln>
               <a:noFill/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
                 </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1872,34 +2292,49 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
               <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="-5400000"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="1" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
+                  <a:rPr lang="en-US"/>
                   <a:t>Number of Transactions</a:t>
                 </a:r>
               </a:p>
@@ -1908,34 +2343,56 @@
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
-            <a:ln w="0">
+            <a:ln>
               <a:noFill/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
                 </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1946,12 +2403,11 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="0">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -1960,15 +2416,32 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
       <a:round/>
     </a:ln>
+    <a:effectLst/>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -1977,20 +2450,1787 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="213">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="236">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="213">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>140805</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>8283</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>152640</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>31680</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>550205</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>48246</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2017,16 +4257,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>149087</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>157370</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>308520</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>31680</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>101455</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>172485</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2053,16 +4293,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>149087</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>149087</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>872640</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>32040</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>118922</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>181127</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2280,24 +4520,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2437,14 +4677,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -3367,38 +5607,38 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
     </row>
     <row r="18" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3416,496 +5656,516 @@
   <dimension ref="A1:AX62"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="14" width="10" customWidth="1"/>
+    <col min="1" max="2" width="16" style="21" customWidth="1"/>
+    <col min="3" max="3" width="10" style="21" customWidth="1"/>
+    <col min="4" max="4" width="12" style="21" customWidth="1"/>
+    <col min="5" max="5" width="16" style="21" customWidth="1"/>
+    <col min="6" max="6" width="6" style="21" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" style="21" customWidth="1"/>
+    <col min="9" max="14" width="10" style="21" customWidth="1"/>
+    <col min="15" max="16384" width="8.7109375" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="20" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="22" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29" t="s">
+      <c r="B5" s="27"/>
+      <c r="C5" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29" t="s">
+      <c r="D5" s="27"/>
+      <c r="E5" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29" t="s">
+      <c r="F5" s="27"/>
+      <c r="G5" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="29"/>
-    </row>
-    <row r="6" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24">
+      <c r="H5" s="27"/>
+    </row>
+    <row r="6" spans="1:8" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="28">
         <f>SUM('Sales Data'!F4:F43)</f>
         <v>189430</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25">
+      <c r="B6" s="28"/>
+      <c r="C6" s="29">
         <f>AVERAGE('Sales Data'!F4:F43)</f>
         <v>4735.75</v>
       </c>
-      <c r="D6" s="25"/>
+      <c r="D6" s="29"/>
       <c r="E6" s="26" t="str">
         <f>INDEX(A9:A12,MATCH(MAX(B9:B12),B9:B12,0))</f>
         <v>Groceries</v>
       </c>
       <c r="F6" s="26"/>
-      <c r="G6" s="27">
+      <c r="G6" s="30">
         <f>COUNTA('Sales Data'!A4:A43)</f>
         <v>40</v>
       </c>
-      <c r="H6" s="27"/>
-    </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="H6" s="30"/>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="31" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="33">
         <f>SUMIF('Sales Data'!$C$4:$C$43,A9,'Sales Data'!$F$4:$F$43)</f>
         <v>96100</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="33">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D9,'Sales Data'!$F$4:$F$43)</f>
         <v>14250</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="34">
         <f>COUNTIFS('Sales Data'!$F$4:$F$43,"&gt;="&amp;0,'Sales Data'!$F$4:$F$43,"&lt;="&amp;2499)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="33">
         <f>SUMIF('Sales Data'!$C$4:$C$43,A10,'Sales Data'!$F$4:$F$43)</f>
         <v>55760</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="33">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D10,'Sales Data'!$F$4:$F$43)</f>
         <v>9650</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="34">
         <f>COUNTIFS('Sales Data'!$F$4:$F$43,"&gt;="&amp;2500,'Sales Data'!$F$4:$F$43,"&lt;="&amp;4999)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="33">
         <f>SUMIF('Sales Data'!$C$4:$C$43,A11,'Sales Data'!$F$4:$F$43)</f>
         <v>23640</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="33">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D11,'Sales Data'!$F$4:$F$43)</f>
         <v>7940</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="34">
         <f>COUNTIFS('Sales Data'!$F$4:$F$43,"&gt;="&amp;5000,'Sales Data'!$F$4:$F$43,"&lt;="&amp;7499)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+    <row r="12" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="33">
         <f>SUMIF('Sales Data'!$C$4:$C$43,A12,'Sales Data'!$F$4:$F$43)</f>
         <v>13930</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="33">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D12,'Sales Data'!$F$4:$F$43)</f>
         <v>13030</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="34">
         <f>COUNTIFS('Sales Data'!$F$4:$F$43,"&gt;="&amp;7500,'Sales Data'!$F$4:$F$43,"&lt;="&amp;9999)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D13" s="10" t="s">
+    <row r="13" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D13" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="33">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D13,'Sales Data'!$F$4:$F$43)</f>
         <v>10100</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="34">
         <f>COUNTIFS('Sales Data'!$F$4:$F$43,"&gt;="&amp;10000,'Sales Data'!$F$4:$F$43,"&lt;="&amp;12499)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D14" s="10" t="s">
+    <row r="14" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D14" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="33">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D14,'Sales Data'!$F$4:$F$43)</f>
         <v>10300</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="34">
         <f>COUNTIFS('Sales Data'!$F$4:$F$43,"&gt;="&amp;12500,'Sales Data'!$F$4:$F$43,"&lt;="&amp;1000000)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="10" t="s">
+    <row r="15" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D15" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="33">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D15,'Sales Data'!$F$4:$F$43)</f>
         <v>13080</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="10" t="s">
+    <row r="16" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D16" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="33">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D16,'Sales Data'!$F$4:$F$43)</f>
         <v>11000</v>
       </c>
     </row>
-    <row r="17" spans="4:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D17" s="10" t="s">
+    <row r="17" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D17" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="33">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D17,'Sales Data'!$F$4:$F$43)</f>
         <v>11080</v>
       </c>
     </row>
-    <row r="18" spans="4:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="10" t="s">
+    <row r="18" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D18" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="33">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D18,'Sales Data'!$F$4:$F$43)</f>
         <v>17400</v>
       </c>
     </row>
-    <row r="19" spans="4:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="10" t="s">
+    <row r="19" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D19" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="33">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D19,'Sales Data'!$F$4:$F$43)</f>
         <v>15900</v>
       </c>
     </row>
-    <row r="20" spans="4:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="10" t="s">
+    <row r="20" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D20" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="33">
         <f>SUMIF('Sales Data'!$B$4:$B$43,D20,'Sales Data'!$F$4:$F$43)</f>
         <v>55700</v>
       </c>
     </row>
-    <row r="40" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H40" s="18" t="s">
+    <row r="21" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="41" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H41" s="20" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="20"/>
-      <c r="N41" s="20"/>
-    </row>
-    <row r="42" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="20"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="20"/>
-      <c r="N42" s="20"/>
-    </row>
-    <row r="43" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="20"/>
-      <c r="N43" s="20"/>
-    </row>
-    <row r="44" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="20"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="20"/>
-      <c r="N44" s="20"/>
-    </row>
-    <row r="45" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-      <c r="M45" s="20"/>
-      <c r="N45" s="20"/>
-    </row>
-    <row r="46" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="20"/>
-      <c r="K46" s="20"/>
-      <c r="L46" s="20"/>
-      <c r="M46" s="20"/>
-      <c r="N46" s="20"/>
-    </row>
-    <row r="47" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="20"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="20"/>
-      <c r="N47" s="20"/>
-    </row>
-    <row r="48" spans="8:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
-      <c r="K48" s="20"/>
-      <c r="L48" s="20"/>
-      <c r="M48" s="20"/>
-      <c r="N48" s="20"/>
-    </row>
-    <row r="49" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
-      <c r="K49" s="20"/>
-      <c r="L49" s="20"/>
-      <c r="M49" s="20"/>
-      <c r="N49" s="20"/>
-    </row>
-    <row r="50" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="20"/>
-      <c r="L50" s="20"/>
-      <c r="M50" s="20"/>
-      <c r="N50" s="20"/>
-    </row>
-    <row r="51" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
-      <c r="J51" s="20"/>
-      <c r="K51" s="20"/>
-      <c r="L51" s="20"/>
-      <c r="M51" s="20"/>
-      <c r="N51" s="20"/>
-    </row>
-    <row r="52" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="20"/>
-      <c r="K52" s="20"/>
-      <c r="L52" s="20"/>
-      <c r="M52" s="20"/>
-      <c r="N52" s="20"/>
-    </row>
-    <row r="53" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="20"/>
-      <c r="K53" s="20"/>
-      <c r="L53" s="20"/>
-      <c r="M53" s="20"/>
-      <c r="N53" s="20"/>
-    </row>
-    <row r="54" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20"/>
-      <c r="L54" s="20"/>
-      <c r="M54" s="20"/>
-      <c r="N54" s="20"/>
-    </row>
-    <row r="55" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-      <c r="J55" s="20"/>
-      <c r="K55" s="20"/>
-      <c r="L55" s="20"/>
-      <c r="M55" s="20"/>
-      <c r="N55" s="20"/>
-    </row>
-    <row r="56" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="18" t="s">
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="24"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="24"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="24"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="24"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="24"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="24"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="24"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="24"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="24"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="24"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+    </row>
+    <row r="40" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="24"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+    </row>
+    <row r="41" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="23" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="20" t="s">
+    <row r="42" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="B57" s="20"/>
-      <c r="C57" s="20"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
-      <c r="F57" s="20"/>
-      <c r="G57" s="20"/>
-    </row>
-    <row r="58" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="20"/>
-      <c r="B58" s="20"/>
-      <c r="C58" s="20"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
-    </row>
-    <row r="59" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="20"/>
-      <c r="B59" s="20"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-    </row>
-    <row r="60" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="20"/>
-      <c r="B60" s="20"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
-    </row>
-    <row r="61" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="20"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="20"/>
-      <c r="E61" s="20"/>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
-    </row>
-    <row r="62" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="20"/>
-      <c r="B62" s="20"/>
-      <c r="C62" s="20"/>
-      <c r="D62" s="20"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="AX62" s="30"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+    </row>
+    <row r="43" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+    </row>
+    <row r="44" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="24"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+    </row>
+    <row r="45" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
+    </row>
+    <row r="46" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="24"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+    </row>
+    <row r="47" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24"/>
+      <c r="B47" s="24"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+    </row>
+    <row r="48" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="50:50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="50:50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="50:50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="50:50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="50:50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="50:50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="50:50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="50:50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="50:50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="50:50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="50:50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="50:50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="50:50" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="50:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AX62" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A42:G47"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A26:G40"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A57:G62"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="H41:N55"/>
   </mergeCells>
   <conditionalFormatting sqref="B9:B12">
-    <cfRule type="dataBar" priority="2">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3919,7 +6179,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E20">
-    <cfRule type="iconSet" priority="3">
+    <cfRule type="iconSet" priority="4">
       <iconSet>
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="33"/>
@@ -3943,6 +6203,22 @@
           </x14:cfRule>
           <xm:sqref>B9:B12</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{91EAE36D-04B0-4179-9A6F-1ED850833CCE}">
+            <x14:iconSet iconSet="3Triangles">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>33</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>67</xm:f>
+              </x14:cfvo>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H9:H14</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
